--- a/master/result/54_穿越成后_命运转折之路/54_穿越成后_命运转折之路.xlsx
+++ b/master/result/54_穿越成后_命运转折之路/54_穿越成后_命运转折之路.xlsx
@@ -397,489 +397,619 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D43"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>royal</v>
       </c>
       <c r="B2" t="str">
-        <v>royal</v>
+        <v>/royal/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>王室的</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>bay</v>
       </c>
       <c r="B3" t="str">
-        <v>bay</v>
+        <v>/bay/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>海湾</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>eight</v>
       </c>
       <c r="B4" t="str">
-        <v>eight</v>
+        <v>/eight/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>八</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>city</v>
       </c>
       <c r="B5" t="str">
-        <v>city</v>
+        <v>/city/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>城市</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dream</v>
       </c>
       <c r="B6" t="str">
-        <v>dream</v>
+        <v>/driːm/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>梦想</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>concerning</v>
       </c>
       <c r="B7" t="str">
-        <v>concerning</v>
+        <v>/concerning/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>关于</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>feast</v>
       </c>
       <c r="B8" t="str">
-        <v>feast</v>
+        <v>/feast/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>宴会</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>appropriate</v>
       </c>
       <c r="B9" t="str">
-        <v>appropriate</v>
+        <v>/appropriate/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>适当的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>hip</v>
       </c>
       <c r="B10" t="str">
-        <v>hip</v>
+        <v>/hip/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>臀部</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>finger</v>
       </c>
       <c r="B11" t="str">
-        <v>finger</v>
+        <v>/finger/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>手指</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>busy</v>
       </c>
       <c r="B12" t="str">
-        <v>busy</v>
+        <v>/ˈbɪzi/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>忙碌的</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>retort</v>
       </c>
       <c r="B13" t="str">
-        <v>retort</v>
+        <v>/retort/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>反驳</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>peach</v>
       </c>
       <c r="B14" t="str">
-        <v>peach</v>
+        <v>/peach/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>桃</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>action</v>
       </c>
       <c r="B15" t="str">
-        <v>action</v>
+        <v>/ˈækʃn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>行动</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>seaside</v>
       </c>
       <c r="B16" t="str">
-        <v>seaside</v>
+        <v>/seaside/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>海滨</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>secret</v>
       </c>
       <c r="B17" t="str">
-        <v>secret</v>
+        <v>/secret/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>秘密</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>port</v>
       </c>
       <c r="B18" t="str">
-        <v>port</v>
+        <v>/port/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>港口</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>agenda</v>
       </c>
       <c r="B19" t="str">
-        <v>agenda</v>
+        <v>/agenda/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>议程</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>philosophy</v>
       </c>
       <c r="B20" t="str">
-        <v>philosophy</v>
+        <v>/philosophy/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>哲学</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>farm</v>
       </c>
       <c r="B21" t="str">
-        <v>farm</v>
+        <v>/farm/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>农场</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>alert</v>
       </c>
       <c r="B22" t="str">
-        <v>alert</v>
+        <v>/alert/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>警觉</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>mobilize</v>
       </c>
       <c r="B23" t="str">
-        <v>mobilize</v>
+        <v>/mobilize/</v>
       </c>
       <c r="C23" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D23" t="str">
         <v>动员</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>quarterly</v>
       </c>
       <c r="B24" t="str">
-        <v>quarterly</v>
+        <v>/quarterly/</v>
       </c>
       <c r="C24" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>季度</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>proposal</v>
       </c>
       <c r="B25" t="str">
-        <v>proposal</v>
+        <v>/proposal/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>提议</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>indifferent</v>
       </c>
       <c r="B26" t="str">
-        <v>indifferent</v>
+        <v>/indifferent/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>冷漠的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>cold</v>
       </c>
       <c r="B27" t="str">
-        <v>cold</v>
+        <v>/kəʊld/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>冷的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>hit</v>
       </c>
       <c r="B28" t="str">
-        <v>hit</v>
+        <v>/hɪt/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>打击</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>spear</v>
       </c>
       <c r="B29" t="str">
-        <v>spear</v>
+        <v>/spear/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>矛</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>vegetarian</v>
       </c>
       <c r="B30" t="str">
-        <v>vegetarian</v>
+        <v>/vegetarian/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>素食者</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>staff</v>
       </c>
       <c r="B31" t="str">
-        <v>staff</v>
+        <v>/staff/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>员工</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>formula</v>
       </c>
       <c r="B32" t="str">
-        <v>formula</v>
+        <v>/formula/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>公式</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>zoom</v>
       </c>
       <c r="B33" t="str">
-        <v>zoom</v>
+        <v>/zoom/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>陡升</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>contaminate</v>
       </c>
       <c r="B34" t="str">
-        <v>contaminate</v>
+        <v>/contaminate/</v>
       </c>
       <c r="C34" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D34" t="str">
         <v>污染</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>plate</v>
       </c>
       <c r="B35" t="str">
-        <v>plate</v>
+        <v>/plate/</v>
       </c>
       <c r="C35" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D35" t="str">
         <v>盘子</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>division</v>
       </c>
       <c r="B36" t="str">
-        <v>division</v>
+        <v>/division/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>部门</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>officer</v>
       </c>
       <c r="B37" t="str">
-        <v>officer</v>
+        <v>/officer/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>官员</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>magnitude</v>
       </c>
       <c r="B38" t="str">
-        <v>magnitude</v>
+        <v>/magnitude/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>规模</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>distribute</v>
       </c>
       <c r="B39" t="str">
-        <v>distribute</v>
+        <v>/dɪˈstrɪbjuːt/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>分配</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>invalid</v>
       </c>
       <c r="B40" t="str">
-        <v>invalid</v>
+        <v>/invalid/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>伤残人</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>flame</v>
       </c>
       <c r="B41" t="str">
-        <v>flame</v>
+        <v>/flame/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>火焰</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>attendance</v>
       </c>
       <c r="B42" t="str">
-        <v>attendance</v>
+        <v>/attendance/</v>
       </c>
       <c r="C42" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>出席</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>evident</v>
       </c>
       <c r="B43" t="str">
-        <v>evident</v>
+        <v>/evident/</v>
       </c>
       <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
         <v>明显的</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
   </ignoredErrors>
 </worksheet>
 </file>